--- a/MONC.MI.xlsx
+++ b/MONC.MI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F967E6BA-8F95-4D63-A391-96C263561CF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7B66262-020B-457C-AA0F-B84BCC48F763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{677D2CEA-1865-4992-A56B-DB953B0C9171}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{677D2CEA-1865-4992-A56B-DB953B0C9171}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="104">
   <si>
     <t>Moncler</t>
   </si>
@@ -348,6 +348,9 @@
   <si>
     <t>H125: Japan only negative performance in Asia</t>
   </si>
+  <si>
+    <t>FY25</t>
+  </si>
 </sst>
 </file>
 
@@ -360,13 +363,19 @@
     <numFmt numFmtId="167" formatCode="0.0%"/>
     <numFmt numFmtId="168" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -555,52 +564,55 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -958,7 +970,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="2">
-        <v>50.68</v>
+        <v>55.15</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
@@ -968,8 +980,8 @@
       <c r="H3" s="3">
         <v>270.522873</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>81</v>
+      <c r="I3" s="32" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
@@ -981,7 +993,7 @@
       </c>
       <c r="H4" s="3">
         <f>H2*H3</f>
-        <v>13710.09920364</v>
+        <v>14919.336445949999</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
@@ -995,8 +1007,8 @@
         <f>1187.978+154.004</f>
         <v>1341.982</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>81</v>
+      <c r="I5" s="32" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
@@ -1007,8 +1019,8 @@
         <f>196.12+761.188+22.828</f>
         <v>980.13599999999997</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>81</v>
+      <c r="I6" s="32" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -1025,7 +1037,7 @@
       </c>
       <c r="H7" s="3">
         <f>H4-H5+H6</f>
-        <v>13348.253203640001</v>
+        <v>14557.490445949999</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
@@ -3161,6 +3173,9 @@
       <c r="Q2" s="4" t="s">
         <v>44</v>
       </c>
+      <c r="R2" s="32" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="3" spans="1:63" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
@@ -3196,6 +3211,9 @@
       <c r="Q3" s="4">
         <v>143</v>
       </c>
+      <c r="R3" s="2">
+        <v>146</v>
+      </c>
     </row>
     <row r="4" spans="1:63" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
@@ -3233,6 +3251,9 @@
       <c r="Q4" s="4">
         <v>96</v>
       </c>
+      <c r="R4" s="2">
+        <v>98</v>
+      </c>
     </row>
     <row r="5" spans="1:63" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
@@ -3268,6 +3289,9 @@
       <c r="Q5" s="4">
         <v>47</v>
       </c>
+      <c r="R5" s="2">
+        <v>51</v>
+      </c>
     </row>
     <row r="6" spans="1:63" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
@@ -3328,6 +3352,10 @@
       <c r="Q6" s="27">
         <f>+SUM(Q3:Q5)</f>
         <v>286</v>
+      </c>
+      <c r="R6" s="27">
+        <f>+SUM(R3:R5)</f>
+        <v>295</v>
       </c>
     </row>
     <row r="7" spans="1:63" x14ac:dyDescent="0.2">
@@ -3364,6 +3392,9 @@
       <c r="Q7" s="4">
         <v>56</v>
       </c>
+      <c r="R7" s="2">
+        <v>49</v>
+      </c>
     </row>
     <row r="8" spans="1:63" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
@@ -3399,6 +3430,9 @@
       <c r="Q8" s="4">
         <v>56</v>
       </c>
+      <c r="R8" s="2">
+        <v>54</v>
+      </c>
     </row>
     <row r="9" spans="1:63" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
@@ -3434,6 +3468,9 @@
       <c r="Q9" s="4">
         <v>27</v>
       </c>
+      <c r="R9" s="2">
+        <v>32</v>
+      </c>
     </row>
     <row r="10" spans="1:63" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
@@ -3469,6 +3506,9 @@
       <c r="Q10" s="4">
         <v>7</v>
       </c>
+      <c r="R10" s="2">
+        <v>9</v>
+      </c>
     </row>
     <row r="11" spans="1:63" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
@@ -3531,7 +3571,10 @@
         <f>+SUM(Q8:Q10)</f>
         <v>90</v>
       </c>
-      <c r="R11" s="1"/>
+      <c r="R11" s="27">
+        <f>+SUM(R8:R10)</f>
+        <v>95</v>
+      </c>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
     </row>
@@ -3569,6 +3612,9 @@
       <c r="Q12" s="4">
         <v>9</v>
       </c>
+      <c r="R12" s="2">
+        <v>11</v>
+      </c>
     </row>
     <row r="13" spans="1:63" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
@@ -3630,6 +3676,10 @@
         <f>+Q11+Q6</f>
         <v>376</v>
       </c>
+      <c r="R13" s="4">
+        <f>+R11+R6</f>
+        <v>390</v>
+      </c>
     </row>
     <row r="14" spans="1:63" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
@@ -3690,6 +3740,10 @@
       <c r="Q14" s="4">
         <f>+Q12+Q7</f>
         <v>65</v>
+      </c>
+      <c r="R14" s="4">
+        <f>+R12+R7</f>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:63" x14ac:dyDescent="0.2">
@@ -3747,7 +3801,9 @@
       <c r="Q16" s="23">
         <v>1378.9549999999999</v>
       </c>
-      <c r="R16" s="23"/>
+      <c r="R16" s="23">
+        <v>1416.039</v>
+      </c>
       <c r="S16" s="23"/>
       <c r="T16" s="23"/>
       <c r="U16" s="23"/>
@@ -3835,7 +3891,9 @@
       <c r="Q17" s="23">
         <v>949.32799999999997</v>
       </c>
-      <c r="R17" s="23"/>
+      <c r="R17" s="23">
+        <v>913.75099999999998</v>
+      </c>
       <c r="S17" s="23"/>
       <c r="T17" s="23"/>
       <c r="U17" s="23"/>
@@ -3921,7 +3979,9 @@
       <c r="Q18" s="23">
         <v>379.03199999999998</v>
       </c>
-      <c r="R18" s="23"/>
+      <c r="R18" s="23">
+        <v>391.14400000000001</v>
+      </c>
       <c r="S18" s="23"/>
       <c r="T18" s="23"/>
       <c r="U18" s="23"/>
@@ -4007,7 +4067,9 @@
       <c r="Q19" s="23">
         <v>2331.8960000000002</v>
       </c>
-      <c r="R19" s="23"/>
+      <c r="R19" s="23">
+        <v>2359.61</v>
+      </c>
       <c r="S19" s="23"/>
       <c r="T19" s="23"/>
       <c r="U19" s="23"/>
@@ -4093,7 +4155,9 @@
       <c r="Q20" s="23">
         <v>375.42</v>
       </c>
-      <c r="R20" s="23"/>
+      <c r="R20" s="23">
+        <v>361.32400000000001</v>
+      </c>
       <c r="S20" s="23"/>
       <c r="T20" s="23"/>
       <c r="U20" s="23"/>
@@ -4179,7 +4243,9 @@
       <c r="Q21" s="23">
         <v>2707.3150000000001</v>
       </c>
-      <c r="R21" s="23"/>
+      <c r="R21" s="23">
+        <v>2720.9340000000002</v>
+      </c>
       <c r="S21" s="23"/>
       <c r="T21" s="23"/>
       <c r="U21" s="23"/>
@@ -4263,7 +4329,9 @@
       <c r="Q22" s="23">
         <v>401.60899999999998</v>
       </c>
-      <c r="R22" s="23"/>
+      <c r="R22" s="23">
+        <v>411.19400000000002</v>
+      </c>
       <c r="S22" s="23"/>
       <c r="T22" s="23"/>
       <c r="U22" s="23"/>
@@ -4347,7 +4415,9 @@
       <c r="Q23" s="25">
         <v>3108.924</v>
       </c>
-      <c r="R23" s="23"/>
+      <c r="R23" s="25">
+        <v>3132.1280000000002</v>
+      </c>
       <c r="S23" s="23"/>
       <c r="T23" s="23"/>
       <c r="U23" s="23"/>
@@ -4431,7 +4501,9 @@
       <c r="Q24" s="23">
         <v>682.36699999999996</v>
       </c>
-      <c r="R24" s="23"/>
+      <c r="R24" s="23">
+        <v>685.93100000000004</v>
+      </c>
       <c r="S24" s="23"/>
       <c r="T24" s="23"/>
       <c r="U24" s="23"/>
@@ -4529,14 +4601,17 @@
         <v>1987.8429999999998</v>
       </c>
       <c r="P25" s="23">
-        <f t="shared" ref="P25:Q25" si="10">+P23-P24</f>
+        <f t="shared" ref="P25:R25" si="10">+P23-P24</f>
         <v>2300.83</v>
       </c>
       <c r="Q25" s="23">
         <f t="shared" si="10"/>
         <v>2426.5569999999998</v>
       </c>
-      <c r="R25" s="23"/>
+      <c r="R25" s="23">
+        <f t="shared" si="10"/>
+        <v>2446.1970000000001</v>
+      </c>
       <c r="S25" s="23"/>
       <c r="T25" s="23"/>
       <c r="U25" s="23"/>
@@ -4620,7 +4695,9 @@
       <c r="Q26" s="23">
         <v>937.34900000000005</v>
       </c>
-      <c r="R26" s="23"/>
+      <c r="R26" s="23">
+        <v>956</v>
+      </c>
       <c r="S26" s="23"/>
       <c r="T26" s="23"/>
       <c r="U26" s="23"/>
@@ -4704,7 +4781,9 @@
       <c r="Q27" s="23">
         <v>351.65600000000001</v>
       </c>
-      <c r="R27" s="23"/>
+      <c r="R27" s="23">
+        <v>357.43200000000002</v>
+      </c>
       <c r="S27" s="23"/>
       <c r="T27" s="23"/>
       <c r="U27" s="23"/>
@@ -4788,7 +4867,9 @@
       <c r="Q28" s="23">
         <v>221.22800000000001</v>
       </c>
-      <c r="R28" s="23"/>
+      <c r="R28" s="23">
+        <v>219.40899999999999</v>
+      </c>
       <c r="S28" s="23"/>
       <c r="T28" s="23"/>
       <c r="U28" s="23"/>
@@ -4870,7 +4951,7 @@
       <c r="J29" s="23"/>
       <c r="K29" s="23"/>
       <c r="L29" s="23">
-        <f t="shared" ref="L29:Q29" si="13">+L25-SUM(L26:L28)</f>
+        <f t="shared" ref="L29:R29" si="13">+L25-SUM(L26:L28)</f>
         <v>491.79899999999998</v>
       </c>
       <c r="M29" s="23">
@@ -4893,7 +4974,10 @@
         <f t="shared" si="13"/>
         <v>916.32399999999961</v>
       </c>
-      <c r="R29" s="23"/>
+      <c r="R29" s="23">
+        <f t="shared" si="13"/>
+        <v>913.35600000000022</v>
+      </c>
       <c r="S29" s="23"/>
       <c r="T29" s="23"/>
       <c r="U29" s="23"/>
@@ -4977,7 +5061,9 @@
       <c r="Q30" s="23">
         <v>28.965</v>
       </c>
-      <c r="R30" s="23"/>
+      <c r="R30" s="23">
+        <v>0</v>
+      </c>
       <c r="S30" s="23"/>
       <c r="T30" s="23"/>
       <c r="U30" s="23"/>
@@ -5061,7 +5147,9 @@
       <c r="Q31" s="23">
         <v>35.479999999999997</v>
       </c>
-      <c r="R31" s="23"/>
+      <c r="R31" s="23">
+        <v>26.184000000000001</v>
+      </c>
       <c r="S31" s="23"/>
       <c r="T31" s="23"/>
       <c r="U31" s="23"/>
@@ -5143,7 +5231,7 @@
       <c r="J32" s="23"/>
       <c r="K32" s="23"/>
       <c r="L32" s="23">
-        <f t="shared" ref="L32:Q32" si="16">+L29+L30-L31</f>
+        <f t="shared" ref="L32:R32" si="16">+L29+L30-L31</f>
         <v>470.72699999999998</v>
       </c>
       <c r="M32" s="23">
@@ -5166,7 +5254,10 @@
         <f t="shared" si="16"/>
         <v>909.80899999999963</v>
       </c>
-      <c r="R32" s="23"/>
+      <c r="R32" s="23">
+        <f t="shared" si="16"/>
+        <v>887.17200000000025</v>
+      </c>
       <c r="S32" s="23"/>
       <c r="T32" s="23"/>
       <c r="U32" s="23"/>
@@ -5250,7 +5341,9 @@
       <c r="Q33" s="23">
         <v>270.21300000000002</v>
       </c>
-      <c r="R33" s="23"/>
+      <c r="R33" s="23">
+        <v>260.50400000000002</v>
+      </c>
       <c r="S33" s="23"/>
       <c r="T33" s="23"/>
       <c r="U33" s="23"/>
@@ -5332,7 +5425,7 @@
       <c r="J34" s="23"/>
       <c r="K34" s="23"/>
       <c r="L34" s="23">
-        <f t="shared" ref="L34:Q34" si="19">+L32-L33</f>
+        <f t="shared" ref="L34:R34" si="19">+L32-L33</f>
         <v>358.69499999999999</v>
       </c>
       <c r="M34" s="23">
@@ -5355,7 +5448,10 @@
         <f t="shared" si="19"/>
         <v>639.59599999999955</v>
       </c>
-      <c r="R34" s="23"/>
+      <c r="R34" s="23">
+        <f t="shared" si="19"/>
+        <v>626.66800000000023</v>
+      </c>
       <c r="S34" s="23"/>
       <c r="T34" s="23"/>
       <c r="U34" s="23"/>
@@ -5439,7 +5535,9 @@
       <c r="Q35" s="23">
         <v>0</v>
       </c>
-      <c r="R35" s="23"/>
+      <c r="R35" s="23">
+        <v>0</v>
+      </c>
       <c r="S35" s="23"/>
       <c r="T35" s="23"/>
       <c r="U35" s="23"/>
@@ -5537,14 +5635,17 @@
         <v>606.69499999999971</v>
       </c>
       <c r="P36" s="23">
-        <f t="shared" ref="P36:Q36" si="22">+P34-P35</f>
+        <f t="shared" ref="P36:R36" si="22">+P34-P35</f>
         <v>611.87299999999982</v>
       </c>
       <c r="Q36" s="23">
         <f t="shared" si="22"/>
         <v>639.59599999999955</v>
       </c>
-      <c r="R36" s="23"/>
+      <c r="R36" s="23">
+        <f t="shared" si="22"/>
+        <v>626.66800000000023</v>
+      </c>
       <c r="S36" s="23"/>
       <c r="T36" s="23"/>
       <c r="U36" s="23"/>
@@ -5705,14 +5806,17 @@
         <v>2.2555873863970843</v>
       </c>
       <c r="P38" s="28">
-        <f t="shared" ref="P38:Q38" si="26">+P36/P39</f>
+        <f t="shared" ref="P38:R38" si="26">+P36/P39</f>
         <v>2.2653029614884161</v>
       </c>
       <c r="Q38" s="28">
         <f t="shared" si="26"/>
         <v>2.3640332956286869</v>
       </c>
-      <c r="R38" s="23"/>
+      <c r="R38" s="28" t="e">
+        <f t="shared" si="26"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="S38" s="23"/>
       <c r="T38" s="23"/>
       <c r="U38" s="23"/>

--- a/MONC.MI.xlsx
+++ b/MONC.MI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7B66262-020B-457C-AA0F-B84BCC48F763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FF90121-D269-4AEF-B4E9-E5B3626F92E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{677D2CEA-1865-4992-A56B-DB953B0C9171}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="110">
   <si>
     <t>Moncler</t>
   </si>
@@ -351,6 +351,24 @@
   <si>
     <t>FY25</t>
   </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
+  <si>
+    <t>Moncler Growth</t>
+  </si>
+  <si>
+    <t>Stone Island Growth</t>
+  </si>
 </sst>
 </file>
 
@@ -363,13 +381,19 @@
     <numFmt numFmtId="167" formatCode="0.0%"/>
     <numFmt numFmtId="168" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -564,52 +588,56 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -970,7 +998,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="2">
-        <v>55.15</v>
+        <v>53.46</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
@@ -980,8 +1008,8 @@
       <c r="H3" s="3">
         <v>270.522873</v>
       </c>
-      <c r="I3" s="32" t="s">
-        <v>83</v>
+      <c r="I3" s="34" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
@@ -993,7 +1021,7 @@
       </c>
       <c r="H4" s="3">
         <f>H2*H3</f>
-        <v>14919.336445949999</v>
+        <v>14462.152790580001</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
@@ -1007,8 +1035,8 @@
         <f>1187.978+154.004</f>
         <v>1341.982</v>
       </c>
-      <c r="I5" s="32" t="s">
-        <v>83</v>
+      <c r="I5" s="34" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
@@ -1019,8 +1047,8 @@
         <f>196.12+761.188+22.828</f>
         <v>980.13599999999997</v>
       </c>
-      <c r="I6" s="32" t="s">
-        <v>83</v>
+      <c r="I6" s="34" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -1037,7 +1065,7 @@
       </c>
       <c r="H7" s="3">
         <f>H4-H5+H6</f>
-        <v>14557.490445949999</v>
+        <v>14100.306790580002</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
@@ -1137,6 +1165,18 @@
       <c r="J2" s="4" t="s">
         <v>83</v>
       </c>
+      <c r="K2" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="L2" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="M2" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="N2" s="34" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
@@ -1158,7 +1198,9 @@
         <v>145</v>
       </c>
       <c r="J3" s="22"/>
-      <c r="K3" s="23"/>
+      <c r="K3" s="22">
+        <v>146</v>
+      </c>
       <c r="L3" s="23"/>
       <c r="M3" s="23"/>
       <c r="N3" s="23"/>
@@ -1195,7 +1237,9 @@
         <v>98</v>
       </c>
       <c r="J4" s="22"/>
-      <c r="K4" s="23"/>
+      <c r="K4" s="22">
+        <v>97</v>
+      </c>
       <c r="L4" s="23"/>
       <c r="M4" s="23"/>
       <c r="N4" s="23"/>
@@ -1232,7 +1276,9 @@
         <v>51</v>
       </c>
       <c r="J5" s="22"/>
-      <c r="K5" s="23"/>
+      <c r="K5" s="22">
+        <v>52</v>
+      </c>
       <c r="L5" s="23"/>
       <c r="M5" s="23"/>
       <c r="N5" s="23"/>
@@ -1270,7 +1316,9 @@
         <v>294</v>
       </c>
       <c r="J6" s="22"/>
-      <c r="K6" s="23"/>
+      <c r="K6" s="22">
+        <v>47</v>
+      </c>
       <c r="L6" s="23"/>
       <c r="M6" s="23"/>
       <c r="N6" s="23"/>
@@ -1322,7 +1370,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K7" s="23"/>
+      <c r="K7" s="22">
+        <f t="shared" ref="K7" si="2">+K6+SUM(K3:K5)</f>
+        <v>342</v>
+      </c>
       <c r="L7" s="23"/>
       <c r="M7" s="23"/>
       <c r="N7" s="23"/>
@@ -1359,7 +1410,9 @@
         <v>54</v>
       </c>
       <c r="J8" s="22"/>
-      <c r="K8" s="23"/>
+      <c r="K8" s="22">
+        <v>53</v>
+      </c>
       <c r="L8" s="23"/>
       <c r="M8" s="23"/>
       <c r="N8" s="23"/>
@@ -1396,7 +1449,9 @@
         <v>31</v>
       </c>
       <c r="J9" s="22"/>
-      <c r="K9" s="23"/>
+      <c r="K9" s="22">
+        <v>33</v>
+      </c>
       <c r="L9" s="23"/>
       <c r="M9" s="23"/>
       <c r="N9" s="23"/>
@@ -1433,7 +1488,9 @@
         <v>7</v>
       </c>
       <c r="J10" s="22"/>
-      <c r="K10" s="23"/>
+      <c r="K10" s="22">
+        <v>8</v>
+      </c>
       <c r="L10" s="23"/>
       <c r="M10" s="23"/>
       <c r="N10" s="23"/>
@@ -1471,7 +1528,9 @@
         <v>92</v>
       </c>
       <c r="J11" s="22"/>
-      <c r="K11" s="23"/>
+      <c r="K11" s="22">
+        <v>11</v>
+      </c>
       <c r="L11" s="23"/>
       <c r="M11" s="23"/>
       <c r="N11" s="23"/>
@@ -1493,19 +1552,19 @@
         <v>98</v>
       </c>
       <c r="C12" s="22">
-        <f t="shared" ref="C12:F12" si="2">+SUM(C8:C11)</f>
+        <f t="shared" ref="C12:F12" si="3">+SUM(C8:C11)</f>
         <v>96</v>
       </c>
       <c r="D12" s="22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E12" s="22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F12" s="22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G12" s="22">
@@ -1516,14 +1575,17 @@
         <v>182</v>
       </c>
       <c r="I12" s="22">
-        <f t="shared" ref="I12:J12" si="3">+SUM(I8:I11)</f>
+        <f t="shared" ref="I12:J12" si="4">+SUM(I8:I11)</f>
         <v>184</v>
       </c>
       <c r="J12" s="22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K12" s="22"/>
+      <c r="K12" s="22">
+        <f t="shared" ref="K12" si="5">+SUM(K8:K11)</f>
+        <v>105</v>
+      </c>
       <c r="L12" s="22"/>
       <c r="M12" s="23"/>
       <c r="N12" s="23"/>
@@ -1545,19 +1607,19 @@
         <v>99</v>
       </c>
       <c r="C13" s="24">
-        <f t="shared" ref="C13:F13" si="4">+C12+C7</f>
+        <f t="shared" ref="C13:F13" si="6">+C12+C7</f>
         <v>427</v>
       </c>
       <c r="D13" s="24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E13" s="24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="F13" s="24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G13" s="24">
@@ -1568,14 +1630,17 @@
         <v>756</v>
       </c>
       <c r="I13" s="24">
-        <f t="shared" ref="I13:J13" si="5">+I12+I7</f>
+        <f t="shared" ref="I13:J13" si="7">+I12+I7</f>
         <v>772</v>
       </c>
       <c r="J13" s="24">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="K13" s="23"/>
+      <c r="K13" s="24">
+        <f t="shared" ref="K13" si="8">+K12+K7</f>
+        <v>447</v>
+      </c>
       <c r="L13" s="23"/>
       <c r="M13" s="23"/>
       <c r="N13" s="23"/>
@@ -1641,7 +1706,9 @@
         <v>226.9</v>
       </c>
       <c r="J15" s="23"/>
-      <c r="K15" s="23"/>
+      <c r="K15" s="23">
+        <v>432.98599999999999</v>
+      </c>
       <c r="L15" s="23"/>
       <c r="M15" s="23"/>
       <c r="N15" s="23"/>
@@ -1681,7 +1748,9 @@
         <v>215.5</v>
       </c>
       <c r="J16" s="23"/>
-      <c r="K16" s="23"/>
+      <c r="K16" s="23">
+        <v>238.48400000000001</v>
+      </c>
       <c r="L16" s="23"/>
       <c r="M16" s="23"/>
       <c r="N16" s="23"/>
@@ -1721,7 +1790,9 @@
         <v>71.8</v>
       </c>
       <c r="J17" s="23"/>
-      <c r="K17" s="23"/>
+      <c r="K17" s="23">
+        <v>95.046000000000006</v>
+      </c>
       <c r="L17" s="23"/>
       <c r="M17" s="23"/>
       <c r="N17" s="23"/>
@@ -1763,7 +1834,9 @@
         <v>514.19999999999993</v>
       </c>
       <c r="J18" s="23"/>
-      <c r="K18" s="23"/>
+      <c r="K18" s="23">
+        <v>766.51599999999996</v>
+      </c>
       <c r="L18" s="23"/>
       <c r="M18" s="23"/>
       <c r="N18" s="23"/>
@@ -1800,7 +1873,9 @@
         <v>21.9</v>
       </c>
       <c r="J19" s="23"/>
-      <c r="K19" s="23"/>
+      <c r="K19" s="23">
+        <v>35.465000000000003</v>
+      </c>
       <c r="L19" s="23"/>
       <c r="M19" s="23"/>
       <c r="N19" s="23"/>
@@ -1837,7 +1912,9 @@
         <v>72.900000000000006</v>
       </c>
       <c r="J20" s="23"/>
-      <c r="K20" s="23"/>
+      <c r="K20" s="23">
+        <v>71.066999999999993</v>
+      </c>
       <c r="L20" s="23"/>
       <c r="M20" s="23"/>
       <c r="N20" s="23"/>
@@ -1874,7 +1951,9 @@
         <v>6.6</v>
       </c>
       <c r="J21" s="23"/>
-      <c r="K21" s="23"/>
+      <c r="K21" s="23">
+        <v>7.5359999999999996</v>
+      </c>
       <c r="L21" s="23"/>
       <c r="M21" s="23"/>
       <c r="N21" s="23"/>
@@ -1916,7 +1995,9 @@
         <v>101.4</v>
       </c>
       <c r="J22" s="23"/>
-      <c r="K22" s="23"/>
+      <c r="K22" s="23">
+        <v>114.068</v>
+      </c>
       <c r="L22" s="23"/>
       <c r="M22" s="23"/>
       <c r="N22" s="23"/>
@@ -1942,34 +2023,37 @@
         <v>818.00800000000004</v>
       </c>
       <c r="D23" s="25">
-        <f t="shared" ref="D23:J23" si="6">+D22+D18</f>
+        <f t="shared" ref="D23:J23" si="9">+D22+D18</f>
         <v>0</v>
       </c>
       <c r="E23" s="25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="F23" s="25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>635.5</v>
       </c>
       <c r="G23" s="25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>829.02200000000005</v>
       </c>
       <c r="H23" s="25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>583.34199999999998</v>
       </c>
       <c r="I23" s="25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>615.59999999999991</v>
       </c>
       <c r="J23" s="25">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="K23" s="23"/>
+      <c r="K23" s="25">
+        <f t="shared" ref="K23" si="10">+K22+K18</f>
+        <v>880.58399999999995</v>
+      </c>
       <c r="L23" s="23"/>
       <c r="M23" s="23"/>
       <c r="N23" s="23"/>
@@ -2013,15 +2097,33 @@
       <c r="Z24" s="22"/>
     </row>
     <row r="25" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="B25" s="33" t="s">
+        <v>64</v>
+      </c>
       <c r="C25" s="23"/>
       <c r="D25" s="23"/>
       <c r="E25" s="23"/>
       <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="23"/>
-      <c r="K25" s="23"/>
+      <c r="G25" s="29">
+        <f t="shared" ref="G25:J25" si="11">+G7/C7-1</f>
+        <v>2.4169184290030232E-2</v>
+      </c>
+      <c r="H25" s="29" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I25" s="29" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J25" s="29" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K25" s="29">
+        <f>+K7/G7-1</f>
+        <v>8.8495575221239076E-3</v>
+      </c>
       <c r="L25" s="23"/>
       <c r="M25" s="23"/>
       <c r="N25" s="23"/>
@@ -2039,15 +2141,33 @@
       <c r="Z25" s="22"/>
     </row>
     <row r="26" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="B26" s="33" t="s">
+        <v>65</v>
+      </c>
       <c r="C26" s="23"/>
       <c r="D26" s="23"/>
       <c r="E26" s="23"/>
       <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="23"/>
-      <c r="I26" s="23"/>
-      <c r="J26" s="23"/>
-      <c r="K26" s="23"/>
+      <c r="G26" s="29">
+        <f t="shared" ref="G26:J26" si="12">+G12/C12-1</f>
+        <v>5.2083333333333259E-2</v>
+      </c>
+      <c r="H26" s="29" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I26" s="29" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J26" s="29" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K26" s="29">
+        <f>+K12/G12-1</f>
+        <v>3.9603960396039639E-2</v>
+      </c>
       <c r="L26" s="23"/>
       <c r="M26" s="23"/>
       <c r="N26" s="23"/>
@@ -2065,15 +2185,33 @@
       <c r="Z26" s="22"/>
     </row>
     <row r="27" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="B27" s="33" t="s">
+        <v>108</v>
+      </c>
       <c r="C27" s="23"/>
       <c r="D27" s="23"/>
       <c r="E27" s="23"/>
       <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
-      <c r="I27" s="23"/>
-      <c r="J27" s="23"/>
-      <c r="K27" s="23"/>
+      <c r="G27" s="29">
+        <f t="shared" ref="G27:J27" si="13">+G18/C18-1</f>
+        <v>2.3794866266468429E-2</v>
+      </c>
+      <c r="H27" s="29" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I27" s="29" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J27" s="29">
+        <f t="shared" si="13"/>
+        <v>-1</v>
+      </c>
+      <c r="K27" s="29">
+        <f>+K18/G18-1</f>
+        <v>6.2011003672971077E-2</v>
+      </c>
       <c r="L27" s="23"/>
       <c r="M27" s="23"/>
       <c r="N27" s="23"/>
@@ -2091,15 +2229,33 @@
       <c r="Z27" s="22"/>
     </row>
     <row r="28" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="B28" s="33" t="s">
+        <v>109</v>
+      </c>
       <c r="C28" s="23"/>
       <c r="D28" s="23"/>
       <c r="E28" s="23"/>
       <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23"/>
-      <c r="J28" s="23"/>
-      <c r="K28" s="23"/>
+      <c r="G28" s="29">
+        <f t="shared" ref="G28:J28" si="14">+G22/C22-1</f>
+        <v>-5.0971475084937712E-2</v>
+      </c>
+      <c r="H28" s="29" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I28" s="29" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J28" s="29">
+        <f t="shared" si="14"/>
+        <v>-1</v>
+      </c>
+      <c r="K28" s="29">
+        <f>+K22/G22-1</f>
+        <v>6.3442193487036391E-2</v>
+      </c>
       <c r="L28" s="23"/>
       <c r="M28" s="23"/>
       <c r="N28" s="23"/>
@@ -2117,15 +2273,33 @@
       <c r="Z28" s="22"/>
     </row>
     <row r="29" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="B29" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="C29" s="23"/>
       <c r="D29" s="23"/>
       <c r="E29" s="23"/>
       <c r="F29" s="23"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="23"/>
-      <c r="I29" s="23"/>
-      <c r="J29" s="23"/>
-      <c r="K29" s="23"/>
+      <c r="G29" s="31">
+        <f t="shared" ref="G29:J29" si="15">+G23/C23-1</f>
+        <v>1.3464415995931622E-2</v>
+      </c>
+      <c r="H29" s="31" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I29" s="31" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J29" s="31">
+        <f t="shared" si="15"/>
+        <v>-1</v>
+      </c>
+      <c r="K29" s="31">
+        <f>+K23/G23-1</f>
+        <v>6.2196178147262637E-2</v>
+      </c>
       <c r="L29" s="23"/>
       <c r="M29" s="23"/>
       <c r="N29" s="23"/>
